--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,521 @@
       <c r="AE6" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260127121738_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9978667.936283389</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3705959.168565743</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3166363.369032038</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3491434.908244176</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7197394.076809919</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3166363.369032038</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-3580444.471031887</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9978667.936283389</v>
+      </c>
+      <c r="N7" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>21302.3664098226</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.396516221105044</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.990999937057495</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9978667.936283389</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9978667.936283389</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128151649_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10783955.47670246</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3705959.168565743</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3491434.908244176</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7197394.076809919</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-2775156.930612814</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3195354.961473318</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10783955.47670246</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>21302.36640982259</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.396516221105044</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.986000061035156</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10783955.47670246</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10783955.47670246</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128151901_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11589243.01712154</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3705959.168565743</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3491434.908244176</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7197394.076809919</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1969869.390193732</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3195354.961473318</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11589243.01712154</v>
+      </c>
+      <c r="N9" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>21302.36640982259</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.396516221105044</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.13700008392334</v>
+      </c>
+      <c r="W9" t="n">
+        <v>11589243.01712154</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11589243.01712154</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128152120_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12394530.55754062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3705959.168565743</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3166363.369032038</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3491434.908244176</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7197394.076809919</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3166363.369032038</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1164581.849774656</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12394530.55754062</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>21302.3664098226</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.396516221105044</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.947999954223633</v>
+      </c>
+      <c r="W10" t="n">
+        <v>12394530.55754062</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12394530.55754062</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128152327_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13199818.09795969</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3705959.168565743</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3491434.908244176</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7197394.076809919</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-359294.3093555804</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3195354.961473318</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13199818.09795969</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>21302.36640982259</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.396516221105044</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.135999917984009</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13199818.09795969</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13199818.09795969</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128152552_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1612,6 +1612,521 @@
       <c r="AE11" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260128152552_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9983828.949428214</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3705913.674800425</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3491413.464952454</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7197327.139752879</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3575216.520830024</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9983828.949428214</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21302.36640982261</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.396516221105043</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.594000101089478</v>
+      </c>
+      <c r="W12" t="n">
+        <v>9983828.949428214</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9983828.949428214</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302220216_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10789116.48984733</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3705913.674800425</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3491413.464952454</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7197327.139752879</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2769928.980410908</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10789116.48984733</v>
+      </c>
+      <c r="N13" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>21302.36640982261</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.396516221105043</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.087000131607056</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10789116.48984733</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10789116.48984733</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302220431_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11594404.03026646</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3705913.674800425</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3491413.464952454</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7197327.139752879</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1964641.439991779</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11594404.03026646</v>
+      </c>
+      <c r="N14" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>21302.36640982261</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.396516221105043</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.127999782562256</v>
+      </c>
+      <c r="W14" t="n">
+        <v>11594404.03026646</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11594404.03026646</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302220652_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12399691.57068551</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3705913.674800425</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3491413.464952454</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7197327.139752879</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1159353.899572732</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12399691.57068551</v>
+      </c>
+      <c r="N15" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>21302.36640982261</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.396516221105043</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.155999898910522</v>
+      </c>
+      <c r="W15" t="n">
+        <v>12399691.57068551</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12399691.57068551</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302220858_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13204979.11110458</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3705913.674800425</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3491413.464952454</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7197327.139752879</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3166363.369032039</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-354066.3591536626</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3195354.961473319</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13204979.11110458</v>
+      </c>
+      <c r="N16" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21304.76292604391</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>21302.36640982261</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.396516221105043</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.277999877929688</v>
+      </c>
+      <c r="W16" t="n">
+        <v>13204979.11110458</v>
+      </c>
+      <c r="X16" t="n">
+        <v>13204979.11110458</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302221129_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,521 @@
       <c r="AE16" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260302221129_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6558439.577374112</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3693872.870432745</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3568970.066946768</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7262842.937379513</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-7043314.151823653</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6558439.577374112</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.534999847412109</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6558439.577374112</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6558439.577374112</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410161522_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7358842.661117831</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3693872.870432745</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3568970.066946768</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7262842.937379513</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-6242911.068079933</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7358842.661117831</v>
+      </c>
+      <c r="N18" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.888999938964844</v>
+      </c>
+      <c r="W18" t="n">
+        <v>7358842.661117831</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7358842.661117831</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410161730_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8159245.744861571</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3693872.870432745</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3568970.066946768</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7262842.937379513</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-5442507.984336194</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8159245.744861571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.02400016784668</v>
+      </c>
+      <c r="W19" t="n">
+        <v>8159245.744861571</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8159245.744861571</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410161941_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8959648.82860527</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3693872.870432745</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3568970.066946768</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7262842.937379513</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4642104.900592495</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8959648.82860527</v>
+      </c>
+      <c r="N20" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.907000064849854</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8959648.82860527</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8959648.82860527</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410162155_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9760051.912348988</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3693872.870432745</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3568970.066946768</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7262842.937379513</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-3841701.816848777</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9760051.912348988</v>
+      </c>
+      <c r="N21" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.878000020980835</v>
+      </c>
+      <c r="W21" t="n">
+        <v>9760051.912348988</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9760051.912348988</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410162400_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2642,6 +2642,521 @@
       <c r="AE21" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260410162400_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-6472547.81410132</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.901999950408936</v>
+      </c>
+      <c r="W22" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191014_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-5672144.730357594</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="N23" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.874000072479248</v>
+      </c>
+      <c r="W23" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191227_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-4871741.646614074</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="N24" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.890999794006348</v>
+      </c>
+      <c r="W24" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="X24" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191431_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-4071338.56287038</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.941999912261963</v>
+      </c>
+      <c r="W25" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191644_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3270935.479126666</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="N26" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.897000074386597</v>
+      </c>
+      <c r="W26" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191851_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3157,6 +3157,521 @@
       <c r="AE26" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260416191851_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-6472547.81410132</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="N27" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.273999929428101</v>
+      </c>
+      <c r="W27" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163045_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-5672144.730357594</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="N28" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.586999893188477</v>
+      </c>
+      <c r="W28" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="X28" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163245_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-4871741.646614074</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="N29" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.746000051498413</v>
+      </c>
+      <c r="W29" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="X29" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163449_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-4071338.56287038</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="N30" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.710999965667725</v>
+      </c>
+      <c r="W30" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="X30" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163654_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-3270935.479126666</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="N31" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.690999984741211</v>
+      </c>
+      <c r="W31" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163854_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE31"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3672,521 @@
       <c r="AE31" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260417163854_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-6472547.81410132</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="N32" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.651000022888184</v>
+      </c>
+      <c r="W32" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8148167.106782516</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425231336_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-5672144.730357594</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M33" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="N33" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.958000183105469</v>
+      </c>
+      <c r="W33" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8948570.190526241</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425231547_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-4871741.646614074</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="N34" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.21999979019165</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9748973.274269762</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425231802_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-4071338.56287038</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="N35" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.049000024795532</v>
+      </c>
+      <c r="W35" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10549376.35801346</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425232022_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3895394.368413404</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8281804.129065584</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-3270935.479126666</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="N36" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.00600004196167</v>
+      </c>
+      <c r="W36" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="X36" t="n">
+        <v>11349779.44175717</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425232230_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA_timeless/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4187,6 +4187,521 @@
       <c r="AE36" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260425232230_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>9540231.944405882</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5287459.206036769</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9673868.96668895</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-6472547.81410132</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9540231.944405882</v>
+      </c>
+      <c r="N37" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.607999801635742</v>
+      </c>
+      <c r="W37" t="n">
+        <v>9540231.944405882</v>
+      </c>
+      <c r="X37" t="n">
+        <v>9540231.944405882</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260427140452_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10340635.02814961</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5287459.206036769</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9673868.96668895</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-5672144.730357594</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M38" t="n">
+        <v>10340635.02814961</v>
+      </c>
+      <c r="N38" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.055999994277954</v>
+      </c>
+      <c r="W38" t="n">
+        <v>10340635.02814961</v>
+      </c>
+      <c r="X38" t="n">
+        <v>10340635.02814961</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260427140704_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11141038.11189313</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5287459.206036769</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9673868.96668895</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-4871741.646614074</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11141038.11189313</v>
+      </c>
+      <c r="N39" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.052000045776367</v>
+      </c>
+      <c r="W39" t="n">
+        <v>11141038.11189313</v>
+      </c>
+      <c r="X39" t="n">
+        <v>11141038.11189313</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260427140922_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>11941441.19563682</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5287459.206036769</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9673868.96668895</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-4071338.56287038</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11941441.19563682</v>
+      </c>
+      <c r="N40" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.013999938964844</v>
+      </c>
+      <c r="W40" t="n">
+        <v>11941441.19563682</v>
+      </c>
+      <c r="X40" t="n">
+        <v>11941441.19563682</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260427141143_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>12741844.27938054</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4386409.760652181</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5287459.206036769</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9673868.96668895</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3160680.568933996</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-3270935.479126666</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3178230.222884256</v>
+      </c>
+      <c r="M41" t="n">
+        <v>12741844.27938054</v>
+      </c>
+      <c r="N41" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>21190.58515856213</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>21188.20148589541</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.383672667163235</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.075999975204468</v>
+      </c>
+      <c r="W41" t="n">
+        <v>12741844.27938054</v>
+      </c>
+      <c r="X41" t="n">
+        <v>12741844.27938054</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA_timeless\20260427141353_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>
